--- a/Data/Building/Corridor.AirQuality.xlsx
+++ b/Data/Building/Corridor.AirQuality.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709603140</v>
+        <v>1712807213</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709777872</v>
+        <v>1712904953</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1711248907</v>
+        <v>1714009396</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1711325482</v>
+        <v>1714092725</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
